--- a/dataset/stats/Ground/Israel_Arcade.xlsx
+++ b/dataset/stats/Ground/Israel_Arcade.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Rank_Info</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Сыграно игр</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Победы</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Процент побед</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Возрождения</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Наземные убийства</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Воздушные убийства</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Морские убийства</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Смерти</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Убийств за возрождение</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Убийств за смерть</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SL за игру</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RP за игру</t>
         </is>
@@ -491,70 +508,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>il_m_51</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>M-51</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>254,736</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>119,320</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>46.8%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>523,550</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>360,318</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>41,561</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>440,841</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>4,508</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>326</t>
         </is>
@@ -563,70 +585,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>il_m48a1_patton_III</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Magach1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.7#2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>74,137</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>33,237</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>44.8%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>86,642</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>48,555</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4,799</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>74,181</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>3,180</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>205</t>
         </is>
@@ -635,70 +662,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>il_amx_13_75</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>AMX-13</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>69,658</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>32,376</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>46.5%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>81,067</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>49,834</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2,902</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>72,719</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2,844</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>198</t>
         </is>
@@ -707,70 +739,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>il_zsu_57_2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>ZSU-57-2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>69,425</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>30,322</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>43.7%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>81,931</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>49,411</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>14,007</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>70,151</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>3,338</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>182</t>
         </is>
@@ -779,70 +816,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>il_merkava_mk_3_raam_segol</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Ra'amSagol</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.3#5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>51,896</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>26,830</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>69,242</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>109,512</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>3,490</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>55,340</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>23,120</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1,743</t>
         </is>
@@ -851,70 +893,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>il_aml_90</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>AML-90</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.3#6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>49,345</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>22,686</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>46.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>55,587</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>26,856</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2,398</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>49,964</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2,664</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>187</t>
         </is>
@@ -923,70 +970,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>il_magach_5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Magach5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>48,420</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>23,667</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>48.9%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>56,109</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>65,218</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2,360</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>45,078</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5,210</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>379</t>
         </is>
@@ -995,70 +1047,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>il_magach_3_idf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Magach3</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#8</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>44,301</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>20,256</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>45.7%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>50,489</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>31,732</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2,548</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>42,186</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>3,428</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>231</t>
         </is>
@@ -1067,70 +1124,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>il_centurion_mk_5_shot</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Sho't</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.7#9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>42,404</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>19,339</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>47,307</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>30,153</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2,911</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>39,657</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>3,414</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>224</t>
         </is>
@@ -1139,70 +1201,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>il_merkava_mk_1b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>MerkavaMk.1B</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.7#10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>40,830</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>19,779</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>48.4%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>45,362</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>48,436</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1,592</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>34,928</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>5,496</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>381</t>
         </is>
@@ -1211,70 +1278,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>il_magach_6a</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Magach6A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>38,529</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>18,063</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>46.9%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>42,061</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>33,831</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2,420</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>33,754</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>4,061</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>279</t>
         </is>
@@ -1283,70 +1355,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>il_m109</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>M109</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#12</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>37,284</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>16,888</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>45.3%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>42,794</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>23,844</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>4,747</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>36,573</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>2,263</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>157</t>
         </is>
@@ -1355,70 +1432,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>il_merkava_mk_3b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>MerkavaMk.3B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.3#13</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>32,499</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>15,219</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>46.8%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>37,369</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>37,402</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>1,247</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>29,758</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>5,749</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>455</t>
         </is>
@@ -1427,70 +1509,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>il_centurion_shot_kal_gimel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Sho'tKalGimel</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#14</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>32,282</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>15,101</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>46.8%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>35,852</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>34,170</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>1,527</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>28,895</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>4,552</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>330</t>
         </is>
@@ -1499,70 +1586,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>il_magach_2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Magach2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.7#15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>32,190</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>14,503</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>45.1%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>36,156</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>21,426</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2,192</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>30,209</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>3,342</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>220</t>
         </is>
@@ -1571,70 +1663,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>il_centurion_shot_kal_alef</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Sho'tKalAlef</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#16</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>31,405</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>14,981</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>34,820</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>27,984</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>1,645</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>28,930</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>4,048</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>286</t>
         </is>
@@ -1643,70 +1740,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>il_merkava_mk_2d</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>MerkavaMk.2D</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Ранг 6БР 10.0#17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>31,295</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>16,133</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>51.6%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>39,350</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>61,309</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1,482</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>30,678</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>20,634</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>1,372</t>
         </is>
@@ -1715,70 +1817,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>il_tiran_4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Tiran4</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>31,038</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>14,493</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>46.7%</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>34,641</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>26,976</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1,420</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>28,489</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>3,650</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>249</t>
         </is>
@@ -1787,70 +1894,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>il_m109a1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Rochev</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>29,417</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>13,282</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>45.2%</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>32,470</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>21,118</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>5,271</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>26,879</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>2,802</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>187</t>
         </is>
@@ -1859,70 +1971,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>il_m113_hvms</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Bardelas/60mmHVMS</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>29,089</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>13,928</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>34,430</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>24,073</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>2,182</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>29,923</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>3,949</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>320</t>
         </is>
@@ -1931,70 +2048,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>il_magach_6r</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Magach6R</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>28,571</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>13,493</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>47.2%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>31,856</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>30,264</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1,400</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>25,828</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>4,595</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2003,70 +2125,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>il_merkava_mk_2b_early</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>MerkavaMk.2B</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.7#22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>26,254</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>12,862</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>28,898</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>35,400</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>990</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>21,661</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>6,220</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>458</t>
         </is>
@@ -2075,70 +2202,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>il_merkava_mk_4m</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>MerkavaMk.4M</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>25,452</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>12,473</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>29,501</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>34,499</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>886</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>24,312</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>6,848</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>540</t>
         </is>
@@ -2147,70 +2279,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>il_namer_rcws_30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Namer30</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.3#24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>25,004</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>11,601</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>46.4%</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>29,150</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>21,153</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>3,420</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>21,469</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>5,089</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>403</t>
         </is>
@@ -2219,70 +2356,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>il_merkava_mk_3c</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>MerkavaMk.3C</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.3#25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>24,554</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>11,870</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>48.3%</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>27,977</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>30,463</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>910</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>22,373</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>6,402</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>518</t>
         </is>
@@ -2291,70 +2433,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>il_merkava_mk_4b</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>MerkavaMk.4B</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>24,230</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>11,664</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>48.1%</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>26,972</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>28,688</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>21,913</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>5,987</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>493</t>
         </is>
@@ -2363,70 +2510,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>il_tiran_6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Tiran6</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>21,386</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>10,375</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>48.5%</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>23,607</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>21,622</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>844</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>19,433</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>4,838</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>351</t>
         </is>
@@ -2435,70 +2587,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>il_sabra_mk1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>SabraMk.I</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.0#28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>20,774</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>10,268</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>49.4%</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>24,345</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>26,675</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>20,371</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>6,403</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>510</t>
         </is>
@@ -2507,70 +2664,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>il_magach_6b_gal_batash</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>GalBatash</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>20,418</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>9,656</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>47.3%</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>22,472</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>21,201</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>763</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>18,348</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>5,047</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>360</t>
         </is>
@@ -2579,70 +2741,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>il_tiran_4_sh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Tiran4S</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>19,535</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>9,112</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>46.6%</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>21,171</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>16,354</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>17,245</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>4,016</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>279</t>
         </is>
@@ -2651,70 +2818,75 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>il_zsu_23_4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ZSU-23-4V</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>17,886</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>7,377</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>41.2%</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>19,196</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>3,737</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>14,133</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>12,748</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>2,737</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>172</t>
         </is>
@@ -2723,70 +2895,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>il_merkava_mk_4_lic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>MerkavaMk.4LIC</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#32</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>17,324</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>8,430</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>18,734</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>22,336</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>581</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>14,429</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>6,436</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>518</t>
         </is>
@@ -2795,70 +2972,75 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>il_magach_6b</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Magach6B</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#33</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>17,207</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>8,633</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>50.2%</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>18,775</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>24,019</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>14,760</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>5,950</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>465</t>
         </is>
@@ -2867,70 +3049,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>il_m163_vulcan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Hovet</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.7#34</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>17,092</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>7,181</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>42.0%</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>18,335</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2,799</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>11,012</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>12,522</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>2,404</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>139</t>
         </is>
@@ -2939,70 +3126,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>il_merkava_mk_1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>MerkavaMk.1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#35</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>15,922</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>7,882</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>49.5%</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>19,167</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>21,564</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>791</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>15,368</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>6,983</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>498</t>
         </is>
@@ -3011,70 +3203,75 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>il_ss_11_halftrack</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>ZachlamTager</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>15,770</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>7,041</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>17,913</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>9,205</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>978</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>15,660</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>2,556</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>165</t>
         </is>
@@ -3083,70 +3280,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>il_tcm_20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>TCM-20</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Ранг 4БР 4.3#37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>14,958</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>6,303</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>42.1%</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>16,308</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>3,006</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>14,140</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>10,187</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>2,227</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>156</t>
         </is>
@@ -3155,70 +3357,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>il_machbet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Machbet</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#38</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>14,556</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>6,095</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>41.9%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>15,921</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2,649</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>16,285</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>10,684</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>1.77</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>3,229</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>203</t>
         </is>
@@ -3227,70 +3434,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>il_magach_6b_gal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Magach6BGal</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#39</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>14,534</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>6,864</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>47.2%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>17,331</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>17,076</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>775</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>14,370</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>5,758</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>467</t>
         </is>
@@ -3299,70 +3511,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>il_magach_6_rocket</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>MagachHydra</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#40</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>14,454</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>7,262</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>50.2%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>16,532</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>21,048</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>14,033</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>6,318</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>502</t>
         </is>
@@ -3371,70 +3588,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>il_namer_tsrikhon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>NamerTsrikhon</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Ранг 8БР 11.3#41</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>12,924</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>6,182</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>47.8%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>14,739</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>11,764</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>1,961</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>10,999</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>5,207</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>496</t>
         </is>
@@ -3443,70 +3665,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>il_magach_6</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Magach6</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#42</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>12,788</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>5,901</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>46.1%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>13,735</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>10,242</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>11,422</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>3,852</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>268</t>
         </is>
@@ -3515,70 +3742,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>il_magach_6m</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Magach6M</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>10,525</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>4,884</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>46.4%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>11,971</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>9,087</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>374</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>10,088</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>4,277</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>311</t>
         </is>
@@ -3587,70 +3819,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>il_m_51_w</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>M-51(W)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#44</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>9,036</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>4,394</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>48.6%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>11,493</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>11,658</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>826</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>9,803</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>11,914</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>782</t>
         </is>
@@ -3659,70 +3896,75 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>il_magach_6c</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Magach6C</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#45</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>8,387</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>3,912</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>46.6%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>9,239</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>8,592</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>367</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>7,462</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>4,943</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>368</t>
         </is>
@@ -3731,70 +3973,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>il_magach_7c</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Magach7C</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>7,596</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>3,703</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>8,246</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>9,014</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>368</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>6,656</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>6,010</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>448</t>
         </is>
@@ -3803,70 +4050,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>il_m113a1_tow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Giraf</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#47</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>7,329</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>3,354</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>45.8%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>8,120</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>3,754</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>7,039</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>3,048</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>201</t>
         </is>
@@ -3875,70 +4127,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>il_mim_72_chaparral</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Imp.Chaparral</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.3#48</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>6,861</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2,965</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>43.2%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>7,679</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>1,678</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>8,157</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>4,833</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>1.28</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>3,339</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>228</t>
         </is>
@@ -3947,70 +4204,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>il_sholef</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Sholef</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.3#49</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>5,479</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>2,640</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>48.2%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>6,415</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>7,406</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>4,037</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>4,651</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>12,960</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>779</t>
         </is>
@@ -4019,70 +4281,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>il_centurion_shot_kal_d</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Sho'tKalDalet</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#50</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>5,479</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>2,668</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>6,649</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>7,485</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>5,549</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>14,638</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>1,045</t>
         </is>
@@ -4091,70 +4358,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>il_magach_3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Magach3(ERA)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#51</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>3,285</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>1,632</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>49.7%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>3,991</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>3,726</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>3,336</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>13,535</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>953</t>
         </is>
@@ -4163,70 +4435,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>il_spyder_aio</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>SPYDER</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#52</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>2,158</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>932</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>43.2%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>2,435</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>2,358</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>1,698</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>3,236</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>174</t>
         </is>
